--- a/model_maker_web_v2/results/Solarize/Solarize_stage1.xlsx
+++ b/model_maker_web_v2/results/Solarize/Solarize_stage1.xlsx
@@ -644,7 +644,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-04-03 15:57</t>
+          <t>2026-04-03 16:03</t>
         </is>
       </c>
     </row>
